--- a/data/trans_orig/P33B5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023</t>
+          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>25604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>46437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>58373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79434</t>
+          <t>81402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87842</t>
+          <t>88724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121679</t>
+          <t>120043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>23780</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17446</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31606</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>29976</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>23293</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>38270</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17884</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31716</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>29976</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>22951</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>39675</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51751</t>
+          <t>52335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>57126</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78552</t>
+          <t>78920</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91452</t>
+          <t>91793</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121670</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>538149</t>
+          <t>536616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>569301</t>
+          <t>568551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>499726</t>
+          <t>498724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>532172</t>
+          <t>530241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1043460</t>
+          <t>1046576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1092814</t>
+          <t>1091193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58599</t>
+          <t>59635</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70162</t>
+          <t>69938</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95280</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>81361</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147541</t>
+          <t>147328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24658</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30737</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>49425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>67810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34022</t>
+          <t>34121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>94417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86073</t>
+          <t>85563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114864</t>
+          <t>115674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108993</t>
+          <t>109911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201454</t>
+          <t>201087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1028408</t>
+          <t>1026049</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1132176</t>
+          <t>1128859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>715917</t>
+          <t>715801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>755902</t>
+          <t>757371</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1749566</t>
+          <t>1748975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1925377</t>
+          <t>1927227</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23112</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>51096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94963</t>
+          <t>95405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43787</t>
+          <t>45522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>30695</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63021</t>
+          <t>62650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>32331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59853</t>
+          <t>61286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>74950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62142</t>
+          <t>60574</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120653</t>
+          <t>120315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>595776</t>
+          <t>598105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>632535</t>
+          <t>634342</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>754096</t>
+          <t>751945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>872696</t>
+          <t>869321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1373479</t>
+          <t>1376107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1508921</t>
+          <t>1492168</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43946</t>
+          <t>44568</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69768</t>
+          <t>70951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81663</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124579</t>
+          <t>127879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136182</t>
+          <t>137923</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187165</t>
+          <t>185518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38404</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39822</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67811</t>
+          <t>67300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42951</t>
+          <t>43884</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69139</t>
+          <t>71131</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66602</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103233</t>
+          <t>103791</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120610</t>
+          <t>122049</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164069</t>
+          <t>165829</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>770891</t>
+          <t>771101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>813534</t>
+          <t>811240</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>846507</t>
+          <t>841663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>916230</t>
+          <t>915430</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1628323</t>
+          <t>1629999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1706630</t>
+          <t>1709134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123270</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187737</t>
+          <t>187787</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244754</t>
+          <t>248519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>338972</t>
+          <t>341741</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399422</t>
+          <t>399588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>511220</t>
+          <t>511483</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77640</t>
+          <t>77600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98196</t>
+          <t>99883</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143353</t>
+          <t>144928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154757</t>
+          <t>158306</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211162</t>
+          <t>211646</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166367</t>
+          <t>159730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>243133</t>
+          <t>242285</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>241716</t>
+          <t>251989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339918</t>
+          <t>339486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>447701</t>
+          <t>445817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>562403</t>
+          <t>569715</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2978480</t>
+          <t>2979668</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3120159</t>
+          <t>3127077</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2860246</t>
+          <t>2856529</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3076003</t>
+          <t>3061141</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5862816</t>
+          <t>5868661</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6093833</t>
+          <t>6120779</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>39129</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25604</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46437</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68396</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>64573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81402</t>
+          <t>89047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103727</t>
+          <t>114499</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88724</t>
+          <t>97653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120043</t>
+          <t>131913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>36352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29976</t>
+          <t>33483</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>42122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52335</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>69893</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>59572</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78920</t>
+          <t>82537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>105790</t>
+          <t>112015</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>95941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>122777</t>
+          <t>128288</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>554079</t>
+          <t>601724</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>536616</t>
+          <t>582725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>568551</t>
+          <t>617532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>516210</t>
+          <t>560630</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>498724</t>
+          <t>542813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>530241</t>
+          <t>577056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1070289</t>
+          <t>1162353</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1046576</t>
+          <t>1138203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1091193</t>
+          <t>1187694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>46070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>34762</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59635</t>
+          <t>61896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82209</t>
+          <t>92929</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69938</t>
+          <t>79544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>108279</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>123003</t>
+          <t>138999</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81361</t>
+          <t>119809</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147328</t>
+          <t>161780</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>42941</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>54697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>53856</t>
+          <t>58209</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>46903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67810</t>
+          <t>72355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69086</t>
+          <t>77505</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94417</t>
+          <t>94518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100075</t>
+          <t>109288</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85563</t>
+          <t>93693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115674</t>
+          <t>124571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>169161</t>
+          <t>186793</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109911</t>
+          <t>164371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201087</t>
+          <t>210358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1068670</t>
+          <t>910075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1026049</t>
+          <t>889241</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1128859</t>
+          <t>933515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>736280</t>
+          <t>825680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>715801</t>
+          <t>803563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>757371</t>
+          <t>848816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1804950</t>
+          <t>1735755</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1748975</t>
+          <t>1703997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1927227</t>
+          <t>1766974</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>40776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>41331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>69445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>75551</t>
+          <t>82660</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>66828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95405</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>37606</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45522</t>
+          <t>48772</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62650</t>
+          <t>71982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>47653</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>64334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>59509</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74950</t>
+          <t>74543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>96044</t>
+          <t>107162</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60574</t>
+          <t>89170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120315</t>
+          <t>128027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>616366</t>
+          <t>706985</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>598105</t>
+          <t>687938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>634342</t>
+          <t>724373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>800332</t>
+          <t>659111</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>751945</t>
+          <t>636755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>869321</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1416698</t>
+          <t>1366095</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376107</t>
+          <t>1334474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1492168</t>
+          <t>1392733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>810994</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>810994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>810994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1635894</t>
+          <t>1613079</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1635894</t>
+          <t>1613079</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1635894</t>
+          <t>1613079</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56375</t>
+          <t>59442</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44568</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70951</t>
+          <t>76550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103944</t>
+          <t>110082</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84415</t>
+          <t>94730</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127879</t>
+          <t>126309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>160320</t>
+          <t>169525</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137923</t>
+          <t>149429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185518</t>
+          <t>190608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>37266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>33710</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>45457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>57278</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>73454</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55471</t>
+          <t>60770</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>47718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71131</t>
+          <t>78001</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>97149</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>82132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103791</t>
+          <t>115446</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>142435</t>
+          <t>157919</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122049</t>
+          <t>138568</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165829</t>
+          <t>180769</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>792125</t>
+          <t>846282</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>771101</t>
+          <t>823123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>811240</t>
+          <t>866218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>872032</t>
+          <t>877378</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>841663</t>
+          <t>852724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>915430</t>
+          <t>898209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1664157</t>
+          <t>1723660</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1629999</t>
+          <t>1691827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1709134</t>
+          <t>1752160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>158650</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123287</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187787</t>
+          <t>200672</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>303951</t>
+          <t>333149</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>248519</t>
+          <t>304805</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>341741</t>
+          <t>362646</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>462601</t>
+          <t>505681</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399588</t>
+          <t>467921</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>511483</t>
+          <t>542602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43843</t>
+          <t>50914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>86033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>141087</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99883</t>
+          <t>123120</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144928</t>
+          <t>160415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>183945</t>
+          <t>206131</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158306</t>
+          <t>183263</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211646</t>
+          <t>232034</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>228051</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159730</t>
+          <t>198538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>242285</t>
+          <t>256728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>305795</t>
+          <t>335839</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251989</t>
+          <t>306691</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>339486</t>
+          <t>364410</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>513430</t>
+          <t>563889</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>445817</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>569715</t>
+          <t>606382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3031240</t>
+          <t>3065066</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2979668</t>
+          <t>3023622</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3127077</t>
+          <t>3107793</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2924853</t>
+          <t>2922798</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2856529</t>
+          <t>2879798</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3061141</t>
+          <t>2963406</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5956093</t>
+          <t>5987863</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5868661</t>
+          <t>5926044</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6120779</t>
+          <t>6042201</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
